--- a/tsmc/dist/20261022_台積電模型_v0.2.xlsx
+++ b/tsmc/dist/20261022_台積電模型_v0.2.xlsx
@@ -117,11 +117,15 @@
     <definedName function="false" hidden="false" name="ni26_2q" vbProcedure="false">In!$E$97</definedName>
     <definedName function="false" hidden="false" name="ni26_3q" vbProcedure="false">In!$E$98</definedName>
     <definedName function="false" hidden="false" name="ni_op" vbProcedure="false">In!$E$133</definedName>
+    <definedName function="false" hidden="false" name="ni_op_2023" vbProcedure="false">NI_OI!$B$20</definedName>
     <definedName function="false" hidden="false" name="ni_op_26" vbProcedure="false">In!$E$122</definedName>
+    <definedName function="false" hidden="false" name="ni_op_alt" vbProcedure="false">NI_OI!$B$22</definedName>
     <definedName function="false" hidden="false" name="ni_op_calc" vbProcedure="false">NI_OI!$B$16</definedName>
     <definedName function="false" hidden="false" name="ni_op_hi" vbProcedure="false">In!$F$133</definedName>
     <definedName function="false" hidden="false" name="ni_op_lo" vbProcedure="false">In!$D$133</definedName>
+    <definedName function="false" hidden="false" name="ni_op_underlying" vbProcedure="false">NI_OI!$B$19</definedName>
     <definedName function="false" hidden="false" name="nonop_hist" vbProcedure="false">NI_OI!$B$15</definedName>
+    <definedName function="false" hidden="false" name="nonop_hist_alt" vbProcedure="false">NI_OI!$B$21</definedName>
     <definedName function="false" hidden="false" name="ntd26" vbProcedure="false">In!$E$103</definedName>
     <definedName function="false" hidden="false" name="ntd26_1q" vbProcedure="false">In!$E$84</definedName>
     <definedName function="false" hidden="false" name="ntd26_2q" vbProcedure="false">In!$E$85</definedName>
@@ -230,7 +234,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="622">
   <si>
     <r>
       <rPr>
@@ -1627,7 +1631,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.887–0.92</t>
+      <t xml:space="preserve">0.864–0.909</t>
     </r>
     <r>
       <rPr>
@@ -12655,7 +12659,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.887</t>
+      <t xml:space="preserve">0.864</t>
     </r>
     <r>
       <rPr>
@@ -12674,35 +12678,92 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">實績比；高 </t>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年扣除一次性利益後的內含水準；高 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.909</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年年度值（稅率上升前、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2022–2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年度最高）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.1.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
     </r>
     <r>
       <rPr>
@@ -12721,26 +12782,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">＝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">v0.1.1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">值（</t>
+      <t xml:space="preserve">（含一次性利益的 </t>
     </r>
     <r>
       <rPr>
@@ -12759,55 +12801,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">單季，含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VIS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">處分利益）。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">v0.1.1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.92</t>
+      <t xml:space="preserve">單季值，不再當上限）</t>
     </r>
   </si>
   <si>
@@ -16283,7 +16277,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.887</t>
+      <t xml:space="preserve">0.864</t>
     </r>
     <r>
       <rPr>
@@ -16332,35 +16326,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.92</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（高；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">v0.1.1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">值）</t>
+      <t xml:space="preserve">0.909</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（高）</t>
     </r>
   </si>
   <si>
@@ -17291,7 +17266,230 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）｜媒體：鏡報（處分世界先進 </t>
+      <t xml:space="preserve">）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SEC 3Q26 6-K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（含 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比較欄）核對營業利益、稅前淨利、淨利相符｜媒體：鉅亨（營業外 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">958.27 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億）；營業利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NT$ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">欄為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Derived</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。一次性項目 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">63.20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的出處見下方「一次性利益出處」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">3Q26</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 Management Report</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（營業外 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34.59</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、稅 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">147.70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、有效稅率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；較 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">降，主因無 </t>
     </r>
     <r>
       <rPr>
@@ -17310,202 +17508,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">股權利益 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">632.0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億）、鉅亨（營業外 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">958.27 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億）；營業利益為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Derived</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">3Q26</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q26 Management Report</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6-K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（營業外 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">34.59</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、稅 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">147.70</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、有效稅率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；較 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">降，主因無 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VIS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">處分與評價利益）；媒體僅有淨利，其餘待複核</t>
+      <t xml:space="preserve">處分與評價利益）｜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SEC 3Q26 6-K a3q26e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（營業利益、稅前淨利、淨利核對相符；使用者提供的核對）</t>
     </r>
   </si>
   <si>
@@ -18224,26 +18246,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">實績比（低值 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.887 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的來源）</t>
+      <t xml:space="preserve">實績比（前版低值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.887</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -18314,7 +18336,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">對照：</t>
+      <t xml:space="preserve">區間低值＝</t>
     </r>
     <r>
       <rPr>
@@ -18341,15 +18363,6 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">約為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -18441,6 +18454,245 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">區間高值＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年年度值（稅率上升前、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2022–2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年度最高）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2022 0.907</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023 0.909</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2024 0.887</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 0.886</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">敏感：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">63.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">若非一次性（不扣除）→ 歷史營業外比率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分子不扣 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">63.2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">敏感：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">63.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">若非一次性 → 基準</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相對基準 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.875 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的變化見 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">README</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">判定：差距兩個來源都有——</t>
     </r>
     <r>
@@ -18673,6 +18925,245 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一次性利益出處（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2Q26 VIS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">處分與評價利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">63.20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">合併財務報告（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SEC 6-K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）載明處分利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NT$63,202,285 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千元，其中含對剩餘持股改按公允價值衡量的非現金重新衡量利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">56,398,783 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千元（喪失重大影響力）；公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-05-15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公告表示近期無進一步出售計畫；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 Management Report </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">說明營業外由 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">95.83 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">降至 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34.59 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主因無該項處分與評價利益；媒體：中央社、東森財經、鉅亨。頁碼：搜尋摘錄未含頁碼，未取得（文件與段落見 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sources </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SEC 3Q26 6-K </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本身未標註一次性項目。</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">來源</t>
   </si>
   <si>
@@ -20035,6 +20526,491 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.ctee.com.tw/news/20260416702066-430502</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NI_OI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：台積電 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">合併財務報告（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SEC 6-K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VIS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">處分利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">63,202,285 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千元）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/0001046179/000104617926000541/a2026q2consolidatedreport-.htm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NI_OI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：台積電出售 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VIS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">股權公告（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SEC 6-K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sec.gov/Archives/edgar/data/0001046179/000104617926000280/tsmctosell81ofvanguardinte.htm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NI_OI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：台積電 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 6-K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（核對 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2Q26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益、稅前淨利、淨利）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NI_OI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：中央社（處分 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VIS 1.52 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億股）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cna.com.tw/news/afe/202605180297.aspx</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NI_OI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：東森財經（估獲利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">632.02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fnc.ebc.net.tw/fncnews/stock/210975</t>
   </si>
   <si>
     <r>
@@ -20323,13 +21299,13 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0"/>
-    <numFmt numFmtId="166" formatCode="0%"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="0.0\x"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0"/>
-    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="0%"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="0.0\x"/>
+    <numFmt numFmtId="171" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -20477,11 +21453,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -20509,7 +21485,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -23491,15 +24467,17 @@
       <c r="C133" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="D133" s="7" t="n">
-        <v>0.887</v>
+      <c r="D133" s="9" t="n">
+        <f aca="false">ni_op_underlying</f>
+        <v>0.864414533026079</v>
       </c>
       <c r="E133" s="8" t="n">
         <f aca="false">(1+nonop_hist)*(1-etr_new)</f>
         <v>0.874593626904623</v>
       </c>
-      <c r="F133" s="7" t="n">
-        <v>0.92</v>
+      <c r="F133" s="9" t="n">
+        <f aca="false">ni_op_2023</f>
+        <v>0.909166874667651</v>
       </c>
       <c r="G133" s="8" t="s">
         <v>119</v>
@@ -23817,16 +24795,16 @@
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>399</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -23837,19 +24815,19 @@
       <c r="A4" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <f aca="false">u_bw_26/pp_GB*1000</f>
         <v>385.714285714286</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="11" t="n">
         <f aca="false">u_bw_27/pp_GB*1000</f>
         <v>171.428571428571</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="11" t="n">
         <f aca="false">u_bw_28*um28_A/pp_GB*1000</f>
         <v>35.7142857142857</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="11" t="n">
         <f aca="false">u_bw_28*(1+g29_bw)*um29_A/pp_GB*1000</f>
         <v>17.8571428571429</v>
       </c>
@@ -23858,19 +24836,19 @@
       <c r="A5" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="11" t="n">
         <f aca="false">u_rb_26/pp_VR*1000</f>
         <v>212.5</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="11" t="n">
         <f aca="false">u_rb_27/pp_VR*1000</f>
         <v>875</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11" t="n">
         <f aca="false">u_rb_28*um28_A/pp_VR*1000</f>
         <v>875</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="11" t="n">
         <f aca="false">u_rb_28*(1+g29_rb)*um29_A/pp_VR*1000</f>
         <v>1006.25</v>
       </c>
@@ -23879,19 +24857,19 @@
       <c r="A6" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <f aca="false">u_ru_26/pp_RU*1000</f>
         <v>0</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <f aca="false">u_ru_27/pp_RU*1000</f>
         <v>75</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <f aca="false">u_ru_28*um28_A/pp_RU*1000</f>
         <v>500</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <f aca="false">u_ru_28*(1+g29_ru)*um29_A/pp_RU*1000</f>
         <v>575</v>
       </c>
@@ -23900,19 +24878,19 @@
       <c r="A7" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <f aca="false">u_hp_26/pp_HP*1000</f>
         <v>17.2413793103448</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="11" t="n">
         <f aca="false">u_hp_27/pp_HP*1000</f>
         <v>0</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="11" t="n">
         <f aca="false">u_hp_28*um28_A/pp_HP*1000</f>
         <v>0</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="11" t="n">
         <f aca="false">u_hp_28*(1+g29_hp)*um29_A/pp_HP*1000</f>
         <v>0</v>
       </c>
@@ -23921,19 +24899,19 @@
       <c r="A8" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <f aca="false">u_amd_26/pp_AMD8*1000</f>
         <v>88.2352941176471</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <f aca="false">u_amd_27/pp_AMDR*1000</f>
         <v>250</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <f aca="false">u_amd_28*um28_A/pp_AMDR*1000</f>
         <v>333.333333333333</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <f aca="false">u_amd_28*(1+g29_amd)*um29_A/pp_AMDR*1000</f>
         <v>383.333333333333</v>
       </c>
@@ -23942,19 +24920,19 @@
       <c r="A9" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <f aca="false">u_tpu_26/pp_TPU7*1000</f>
         <v>137.5</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="n">
         <f aca="false">u_tpu_27/pp_TPU8*1000</f>
         <v>229.166666666667</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="11" t="n">
         <f aca="false">u_tpu_28*um28_A/pp_TPU8*1000</f>
         <v>291.666666666667</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="11" t="n">
         <f aca="false">u_tpu_28*(1+g29_tpu)*um29_A/pp_TPU8*1000</f>
         <v>335.416666666667</v>
       </c>
@@ -23963,19 +24941,19 @@
       <c r="A10" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <f aca="false">u_trn_26/pp_TRN*1000</f>
         <v>66.6666666666667</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="11" t="n">
         <f aca="false">u_trn_27/pp_TRN*1000</f>
         <v>83.3333333333333</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <f aca="false">u_trn_28*um28_A/pp_TRN*1000</f>
         <v>100</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="11" t="n">
         <f aca="false">u_trn_28*(1+g29_trn)*um29_A/pp_TRN*1000</f>
         <v>115</v>
       </c>
@@ -23984,19 +24962,19 @@
       <c r="A11" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <f aca="false">u_oth_26/pp_ASIC*1000</f>
         <v>50</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <f aca="false">u_oth_27/pp_ASIC*1000</f>
         <v>225</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11" t="n">
         <f aca="false">u_oth_28*um28_A/pp_ASIC*1000</f>
         <v>250</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <f aca="false">u_oth_28*(1+g29_oth)*um29_A/pp_ASIC*1000</f>
         <v>287.5</v>
       </c>
@@ -24005,19 +24983,19 @@
       <c r="A12" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="11" t="n">
         <f aca="false">cow_oth26</f>
         <v>150</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="11" t="n">
         <f aca="false">B12*(1+cow_oth_g)</f>
         <v>187.5</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="11" t="n">
         <f aca="false">C12*(1+cow_oth_g)</f>
         <v>234.375</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="11" t="n">
         <f aca="false">D12*(1+cow_oth_g)</f>
         <v>292.96875</v>
       </c>
@@ -24026,19 +25004,19 @@
       <c r="A13" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="11" t="n">
         <f aca="false">SUM(B4:B12)</f>
         <v>1107.85762580894</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="11" t="n">
         <f aca="false">SUM(C4:C12)</f>
         <v>2096.42857142857</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="11" t="n">
         <f aca="false">SUM(D4:D12)</f>
         <v>2620.08928571429</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="11" t="n">
         <f aca="false">SUM(E4:E12)</f>
         <v>3013.32589285714</v>
       </c>
@@ -24047,19 +25025,19 @@
       <c r="A14" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="11" t="n">
         <f aca="false">B4+B5+B6+B7</f>
         <v>615.455665024631</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="11" t="n">
         <f aca="false">C4+C5+C6+C7</f>
         <v>1121.42857142857</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <f aca="false">D4+D5+D6+D7</f>
         <v>1410.71428571429</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="11" t="n">
         <f aca="false">E4+E5+E6+E7</f>
         <v>1599.10714285714</v>
       </c>
@@ -24068,19 +25046,19 @@
       <c r="A15" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <f aca="false">(cap_end25+cap_end26)/2*12</f>
         <v>1245</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="11" t="n">
         <f aca="false">(cap_end26+cap_end27)/2*12</f>
         <v>1980</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="11" t="n">
         <f aca="false">(cap_end27+cap_end28)/2*12</f>
         <v>2760</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="11" t="n">
         <f aca="false">(cap_end28+cap_end29)/2*12</f>
         <v>3480</v>
       </c>
@@ -24089,19 +25067,19 @@
       <c r="A16" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="11" t="n">
         <f aca="false">B15*(1+osat)</f>
         <v>1369.5</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="11" t="n">
         <f aca="false">C15*(1+osat)</f>
         <v>2178</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="11" t="n">
         <f aca="false">D15*(1+osat)</f>
         <v>3036</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="11" t="n">
         <f aca="false">E15*(1+osat)</f>
         <v>3828</v>
       </c>
@@ -24110,19 +25088,19 @@
       <c r="A17" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="12" t="n">
         <f aca="false">B13/B16</f>
         <v>0.808950438706787</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <f aca="false">C13/C16</f>
         <v>0.962547553456644</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <f aca="false">D13/D16</f>
         <v>0.863007011104837</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <f aca="false">E13/E16</f>
         <v>0.787180222794447</v>
       </c>
@@ -24134,7 +25112,7 @@
       <c r="A18" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="12" t="n">
         <f aca="false">hbm_gap27</f>
         <v>0.21</v>
       </c>
@@ -24146,11 +25124,11 @@
       <c r="A19" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="11" t="n">
         <f aca="false">ms_dem26</f>
         <v>1394</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="11" t="n">
         <f aca="false">ms_dem27</f>
         <v>2509</v>
       </c>
@@ -24159,11 +25137,11 @@
       <c r="A20" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="12" t="n">
         <f aca="false">B13/B19-1</f>
         <v>-0.205267126392436</v>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="12" t="n">
         <f aca="false">C13/C19-1</f>
         <v>-0.16443659966976</v>
       </c>
@@ -24172,11 +25150,11 @@
       <c r="A21" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="12" t="n">
         <f aca="false">B14/660-1</f>
         <v>-0.0674914166293474</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="12" t="n">
         <f aca="false">C14/1222-1</f>
         <v>-0.082300678045359</v>
       </c>
@@ -24213,34 +25191,34 @@
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="10" t="s">
         <v>430</v>
       </c>
     </row>
@@ -24248,43 +25226,43 @@
       <c r="A4" s="0" t="s">
         <v>431</v>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="13" t="n">
         <f aca="false">(u_bw_26*ct_GB+u_rb_26*ct_VR+u_ru_26*ct_RU+u_hp_26*ct_HP+u_amd_26*ct_AMD8+u_tpu_26*ct_TPU7+u_trn_26*ct_TRN+u_oth_26*ct_ASIC)*1</f>
         <v>28.605</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="13" t="n">
         <f aca="false">(u_bw_27*ct_GB+u_rb_27*ct_VR+u_ru_27*ct_RU+u_hp_27*ct_HP+u_amd_27*ct_AMDR+u_tpu_27*ct_TPU8+u_trn_27*ct_TRN+u_oth_27*ct_ASIC)*(1+px27)</f>
         <v>55.6864</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="13" t="n">
         <f aca="false">(u_bw_28*um28_A*ct_GB+u_rb_28*um28_A*ct_VR+u_ru_28*um28_A*ct_RU+u_hp_28*um28_A*ct_HP+u_amd_28*um28_A*ct_AMDR+u_tpu_28*um28_A*ct_TPU8+u_trn_28*um28_A*ct_TRN+u_oth_28*um28_A*ct_ASIC)*(1+px27)*(1+px28)</f>
         <v>73.72512</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <f aca="false">(u_bw_28*(1+g29_bw)*um29_A*ct_GB+u_rb_28*(1+g29_rb)*um29_A*ct_VR+u_ru_28*(1+g29_ru)*um29_A*ct_RU+u_hp_28*(1+g29_hp)*um29_A*ct_HP+u_amd_28*(1+g29_amd)*um29_A*ct_AMDR+u_tpu_28*(1+g29_tpu)*um29_A*ct_TPU8+u_trn_28*(1+g29_trn)*um29_A*ct_TRN+u_oth_28*(1+g29_oth)*um29_A*ct_ASIC)*(1+px27)*(1+px28)*(1+px29)</f>
         <v>88.0736976</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="13" t="n">
         <f aca="false">(u_bw_27*ct_GB+u_rb_27*ct_VR+u_ru_27*ct_RU+u_hp_27*ct_HP+u_amd_27*ct_AMDR+u_tpu_27*ct_TPU8+u_trn_27*ct_TRN+u_oth_27*ct_ASIC)*(1+px27)</f>
         <v>55.6864</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="13" t="n">
         <f aca="false">(u_bw_28*um28_B*ct_GB+u_rb_28*um28_B*ct_VR+u_ru_28*um28_B*ct_RU+u_hp_28*um28_B*ct_HP+u_amd_28*um28_B*ct_AMDR+u_tpu_28*um28_B*ct_TPU8+u_trn_28*um28_B*ct_TRN+u_oth_28*um28_B*ct_ASIC)*(1+px27)*(1+px28)</f>
         <v>58.980096</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="13" t="n">
         <f aca="false">(u_bw_28*(1+g29_bw)*um29_B*ct_GB+u_rb_28*(1+g29_rb)*um29_B*ct_VR+u_ru_28*(1+g29_ru)*um29_B*ct_RU+u_hp_28*(1+g29_hp)*um29_B*ct_HP+u_amd_28*(1+g29_amd)*um29_B*ct_AMDR+u_tpu_28*(1+g29_tpu)*um29_B*ct_TPU8+u_trn_28*(1+g29_trn)*um29_B*ct_TRN+u_oth_28*(1+g29_oth)*um29_B*ct_ASIC)*(1+px27)*(1+px28)*(1+px29)</f>
         <v>74.86264296</v>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="13" t="n">
         <f aca="false">(u_bw_27*ct_GB+u_rb_27*ct_VR+u_ru_27*ct_RU+u_hp_27*ct_HP+u_amd_27*ct_AMDR+u_tpu_27*ct_TPU8+u_trn_27*ct_TRN+u_oth_27*ct_ASIC)*(1+px27)</f>
         <v>55.6864</v>
       </c>
-      <c r="J4" s="12" t="n">
+      <c r="J4" s="13" t="n">
         <f aca="false">(u_bw_28*um28_C*ct_GB+u_rb_28*um28_C*ct_VR+u_ru_28*um28_C*ct_RU+u_hp_28*um28_C*ct_HP+u_amd_28*um28_C*ct_AMDR+u_tpu_28*um28_C*ct_TPU8+u_trn_28*um28_C*ct_TRN+u_oth_28*um28_C*ct_ASIC)*(1+px27)*(1+px28)</f>
         <v>44.235072</v>
       </c>
-      <c r="K4" s="12" t="n">
+      <c r="K4" s="13" t="n">
         <f aca="false">(u_bw_28*(1+g29_bw)*um29_C*ct_GB+u_rb_28*(1+g29_rb)*um29_C*ct_VR+u_ru_28*(1+g29_ru)*um29_C*ct_RU+u_hp_28*(1+g29_hp)*um29_C*ct_HP+u_amd_28*(1+g29_amd)*um29_C*ct_AMDR+u_tpu_28*(1+g29_tpu)*um29_C*ct_TPU8+u_trn_28*(1+g29_trn)*um29_C*ct_TRN+u_oth_28*(1+g29_oth)*um29_C*ct_ASIC)*(1+px27)*(1+px28)*(1+px29)</f>
         <v>52.84421856</v>
       </c>
@@ -24293,43 +25271,43 @@
       <c r="A5" s="0" t="s">
         <v>432</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="13" t="n">
         <f aca="false">B4*(1+ai_oth)</f>
         <v>34.326</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="13" t="n">
         <f aca="false">C4*(1+ai_oth)</f>
         <v>66.82368</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <f aca="false">D4*(1+ai_oth)</f>
         <v>88.470144</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <f aca="false">E4*(1+ai_oth)</f>
         <v>105.68843712</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="13" t="n">
         <f aca="false">F4*(1+ai_oth)</f>
         <v>66.82368</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="13" t="n">
         <f aca="false">G4*(1+ai_oth)</f>
         <v>70.7761152</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="13" t="n">
         <f aca="false">H4*(1+ai_oth)</f>
         <v>89.835171552</v>
       </c>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="13" t="n">
         <f aca="false">I4*(1+ai_oth)</f>
         <v>66.82368</v>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="13" t="n">
         <f aca="false">J4*(1+ai_oth)</f>
         <v>53.0820864</v>
       </c>
-      <c r="K5" s="12" t="n">
+      <c r="K5" s="13" t="n">
         <f aca="false">K4*(1+ai_oth)</f>
         <v>63.413062272</v>
       </c>
@@ -24338,43 +25316,43 @@
       <c r="A6" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <f aca="false">B7-B5</f>
         <v>141.794</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <f aca="false">B6*(1+na27_A)</f>
         <v>158.80928</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <f aca="false">C6*(1+na28_A)</f>
         <v>174.690208</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <f aca="false">D6*(1+na29_A)</f>
         <v>188.66542464</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <f aca="false">B6*(1+na27_B)</f>
         <v>158.80928</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="13" t="n">
         <f aca="false">F6*(1+na28_B)</f>
         <v>166.749744</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="13" t="n">
         <f aca="false">G6*(1+na29_B)</f>
         <v>171.75223632</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="13" t="n">
         <f aca="false">B6*(1+na27_C)</f>
         <v>158.80928</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="13" t="n">
         <f aca="false">I6*(1+na28_C)</f>
         <v>158.80928</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="13" t="n">
         <f aca="false">J6*(1+na29_C)</f>
         <v>154.0450016</v>
       </c>
@@ -24383,43 +25361,43 @@
       <c r="A7" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <f aca="false">rev26</f>
         <v>176.12</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="13" t="n">
         <f aca="false">C5+C6</f>
         <v>225.63296</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <f aca="false">D5+D6</f>
         <v>263.160352</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <f aca="false">E5+E6</f>
         <v>294.35386176</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="13" t="n">
         <f aca="false">F5+F6</f>
         <v>225.63296</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <f aca="false">G5+G6</f>
         <v>237.5258592</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="13" t="n">
         <f aca="false">H5+H6</f>
         <v>261.587407872</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="13" t="n">
         <f aca="false">I5+I6</f>
         <v>225.63296</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="13" t="n">
         <f aca="false">J5+J6</f>
         <v>211.8913664</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K7" s="13" t="n">
         <f aca="false">K5+K6</f>
         <v>217.458063872</v>
       </c>
@@ -24428,43 +25406,43 @@
       <c r="A8" s="0" t="s">
         <v>435</v>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <f aca="false">B5/B7</f>
         <v>0.194901203724733</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <f aca="false">C5/C7</f>
         <v>0.296160986409078</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <f aca="false">D5/D7</f>
         <v>0.336183408053809</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <f aca="false">E5/E7</f>
         <v>0.359052320523563</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <f aca="false">F5/F7</f>
         <v>0.296160986409078</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <f aca="false">G5/G7</f>
         <v>0.297972252109214</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="14" t="n">
         <f aca="false">H5/H7</f>
         <v>0.343423149771636</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="14" t="n">
         <f aca="false">I5/I7</f>
         <v>0.296160986409078</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="14" t="n">
         <f aca="false">J5/J7</f>
         <v>0.250515569850042</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="14" t="n">
         <f aca="false">K5/K7</f>
         <v>0.291610534660725</v>
       </c>
@@ -24473,43 +25451,43 @@
       <c r="A9" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <f aca="false">gm26</f>
         <v>0.665334900583875</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <f aca="false">gm27_A</f>
         <v>0.64</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <f aca="false">gm28_A</f>
         <v>0.63</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <f aca="false">gm29_A</f>
         <v>0.62</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="14" t="n">
         <f aca="false">gm27_B</f>
         <v>0.64</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="14" t="n">
         <f aca="false">gm28_B</f>
         <v>0.58</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="14" t="n">
         <f aca="false">gm29_B</f>
         <v>0.56</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="14" t="n">
         <f aca="false">gm27_C</f>
         <v>0.64</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="14" t="n">
         <f aca="false">gm28_C</f>
         <v>0.54</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="14" t="n">
         <f aca="false">gm29_C</f>
         <v>0.52</v>
       </c>
@@ -24518,43 +25496,43 @@
       <c r="A10" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <f aca="false">B7*B9</f>
         <v>117.178782690832</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="13" t="n">
         <f aca="false">C7*C9</f>
         <v>144.4050944</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="13" t="n">
         <f aca="false">D7*D9</f>
         <v>165.79102176</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="13" t="n">
         <f aca="false">E7*E9</f>
         <v>182.4993942912</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="13" t="n">
         <f aca="false">F7*F9</f>
         <v>144.4050944</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="13" t="n">
         <f aca="false">G7*G9</f>
         <v>137.764998336</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="13" t="n">
         <f aca="false">H7*H9</f>
         <v>146.48894840832</v>
       </c>
-      <c r="I10" s="12" t="n">
+      <c r="I10" s="13" t="n">
         <f aca="false">I7*I9</f>
         <v>144.4050944</v>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="J10" s="13" t="n">
         <f aca="false">J7*J9</f>
         <v>114.421337856</v>
       </c>
-      <c r="K10" s="12" t="n">
+      <c r="K10" s="13" t="n">
         <f aca="false">K7*K9</f>
         <v>113.07819321344</v>
       </c>
@@ -24563,43 +25541,43 @@
       <c r="A11" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <f aca="false">B7*(B9-opex_26)</f>
         <v>103.167777161</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="13" t="n">
         <f aca="false">C7*(C9-opex)</f>
         <v>127.4826224</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <f aca="false">D7*(D9-opex)</f>
         <v>146.05399536</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <f aca="false">E7*(E9-opex)</f>
         <v>160.4228546592</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="13" t="n">
         <f aca="false">F7*(F9-opex)</f>
         <v>127.4826224</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="13" t="n">
         <f aca="false">G7*(G9-opex)</f>
         <v>119.950558896</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="13" t="n">
         <f aca="false">H7*(H9-opex)</f>
         <v>126.86989281792</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="I11" s="13" t="n">
         <f aca="false">I7*(I9-opex)</f>
         <v>127.4826224</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="13" t="n">
         <f aca="false">J7*(J9-opex)</f>
         <v>98.529485376</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="K11" s="13" t="n">
         <f aca="false">K7*(K9-opex)</f>
         <v>96.76883842304</v>
       </c>
@@ -24608,43 +25586,43 @@
       <c r="A12" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <f aca="false">B11*ni_op_26</f>
         <v>91.5171592342628</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="13" t="n">
         <f aca="false">C11*ni_op</f>
         <v>111.495489092129</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="13" t="n">
         <f aca="false">D11*ni_op</f>
         <v>127.737893525813</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="13" t="n">
         <f aca="false">E11*ni_op</f>
         <v>140.304806294783</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="13" t="n">
         <f aca="false">F11*ni_op</f>
         <v>111.495489092129</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="13" t="n">
         <f aca="false">G11*ni_op</f>
         <v>104.907994354089</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="13" t="n">
         <f aca="false">H11*ni_op</f>
         <v>110.959599704625</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" s="13" t="n">
         <f aca="false">I11*ni_op</f>
         <v>111.495489092129</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="J12" s="13" t="n">
         <f aca="false">J11*ni_op</f>
         <v>86.1732599720419</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="K12" s="13" t="n">
         <f aca="false">K11*ni_op</f>
         <v>84.633409367754</v>
       </c>
@@ -24653,43 +25631,43 @@
       <c r="A13" s="0" t="s">
         <v>440</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <f aca="false">B12*fx_26/shares</f>
         <v>112.095299667786</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="13" t="n">
         <f aca="false">C12*fx/shares</f>
         <v>137.595667217436</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <f aca="false">D12*fx/shares</f>
         <v>157.640285107059</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="13" t="n">
         <f aca="false">E12*fx/shares</f>
         <v>173.149008925301</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="13" t="n">
         <f aca="false">F12*fx/shares</f>
         <v>137.595667217436</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="13" t="n">
         <f aca="false">G12*fx/shares</f>
         <v>129.466094073693</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="13" t="n">
         <f aca="false">H12*fx/shares</f>
         <v>136.934330526341</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I13" s="13" t="n">
         <f aca="false">I12*fx/shares</f>
         <v>137.595667217436</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="13" t="n">
         <f aca="false">J12*fx/shares</f>
         <v>106.34571226785</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="K13" s="13" t="n">
         <f aca="false">K12*fx/shares</f>
         <v>104.445395286083</v>
       </c>
@@ -24698,43 +25676,43 @@
       <c r="A14" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="15" t="n">
         <f aca="false">px/B13</f>
         <v>23.0607349965708</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="15" t="n">
         <f aca="false">px/C13</f>
         <v>18.7869287767256</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <f aca="false">px/D13</f>
         <v>16.3980926464605</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <f aca="false">px/E13</f>
         <v>14.9293375459932</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="15" t="n">
         <f aca="false">px/F13</f>
         <v>18.7869287767256</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="15" t="n">
         <f aca="false">px/G13</f>
         <v>19.9666176576595</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="15" t="n">
         <f aca="false">px/H13</f>
         <v>18.8776619425086</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I14" s="15" t="n">
         <f aca="false">px/I13</f>
         <v>18.7869287767256</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="15" t="n">
         <f aca="false">px/J13</f>
         <v>24.3075150363302</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="15" t="n">
         <f aca="false">px/K13</f>
         <v>24.749774682929</v>
       </c>
@@ -24743,43 +25721,43 @@
       <c r="A15" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <f aca="false">capex26</f>
         <v>62</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="13" t="n">
         <f aca="false">capex27</f>
         <v>77</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <f aca="false">capex28</f>
         <v>90</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="13" t="n">
         <f aca="false">capex29</f>
         <v>95</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="13" t="n">
         <f aca="false">capex27</f>
         <v>77</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="13" t="n">
         <f aca="false">capex28</f>
         <v>90</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="13" t="n">
         <f aca="false">capex29</f>
         <v>95</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="13" t="n">
         <f aca="false">capex27</f>
         <v>77</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="13" t="n">
         <f aca="false">capex28</f>
         <v>90</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="K15" s="13" t="n">
         <f aca="false">capex29</f>
         <v>95</v>
       </c>
@@ -24788,43 +25766,43 @@
       <c r="A16" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="13" t="n">
         <f aca="false">B12-B15</f>
         <v>29.5171592342628</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="13" t="n">
         <f aca="false">C12-C15</f>
         <v>34.4954890921285</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <f aca="false">D12-D15</f>
         <v>37.7378935258134</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="13" t="n">
         <f aca="false">E12-E15</f>
         <v>45.3048062947829</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="13" t="n">
         <f aca="false">F12-F15</f>
         <v>34.4954890921285</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="13" t="n">
         <f aca="false">G12-G15</f>
         <v>14.9079943540892</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="H16" s="13" t="n">
         <f aca="false">H12-H15</f>
         <v>15.9595997046254</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" s="13" t="n">
         <f aca="false">I12-I15</f>
         <v>34.4954890921285</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="J16" s="13" t="n">
         <f aca="false">J12-J15</f>
         <v>-3.82674002795815</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="K16" s="13" t="n">
         <f aca="false">K12-K15</f>
         <v>-10.366590632246</v>
       </c>
@@ -24873,13 +25851,13 @@
       <c r="B3" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>448</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>450</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -24903,15 +25881,15 @@
       <c r="D4" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <f aca="false">PL!C13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="11" t="n">
         <f aca="false">B4*E4</f>
         <v>2063.93500826154</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="12" t="n">
         <f aca="false">F4/px-1</f>
         <v>-0.201572530653177</v>
       </c>
@@ -24930,15 +25908,15 @@
       <c r="D5" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <f aca="false">PL!C13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="11" t="n">
         <f aca="false">B5*E5</f>
         <v>2820.71117795744</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="12" t="n">
         <f aca="false">F5/px-1</f>
         <v>0.0911842081073253</v>
       </c>
@@ -24957,15 +25935,15 @@
       <c r="D6" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <f aca="false">PL!C13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <f aca="false">B6*E6</f>
         <v>4499.37831801015</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <f aca="false">F6/px-1</f>
         <v>0.740571883176075</v>
       </c>
@@ -24984,15 +25962,15 @@
       <c r="D7" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <f aca="false">PL!D13</f>
         <v>157.640285107059</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="11" t="n">
         <f aca="false">B7*E7</f>
         <v>2364.60427660588</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <f aca="false">F7/px-1</f>
         <v>-0.0852594674638768</v>
       </c>
@@ -25011,15 +25989,15 @@
       <c r="D8" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="13" t="n">
         <f aca="false">PL!D13</f>
         <v>157.640285107059</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <f aca="false">B8*E8</f>
         <v>3231.6258446947</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <f aca="false">F8/px-1</f>
         <v>0.250145394466035</v>
       </c>
@@ -25038,15 +26016,15 @@
       <c r="D9" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <f aca="false">PL!D13</f>
         <v>157.640285107059</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="11" t="n">
         <f aca="false">B9*E9</f>
         <v>5154.83732300082</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="12" t="n">
         <f aca="false">F9/px-1</f>
         <v>0.994134360928749</v>
       </c>
@@ -25065,15 +26043,15 @@
       <c r="D10" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="13" t="n">
         <f aca="false">PL!F13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="11" t="n">
         <f aca="false">B10*E10</f>
         <v>2063.93500826154</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="12" t="n">
         <f aca="false">F10/px-1</f>
         <v>-0.201572530653177</v>
       </c>
@@ -25092,15 +26070,15 @@
       <c r="D11" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <f aca="false">PL!F13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="11" t="n">
         <f aca="false">B11*E11</f>
         <v>2820.71117795744</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="12" t="n">
         <f aca="false">F11/px-1</f>
         <v>0.0911842081073253</v>
       </c>
@@ -25119,15 +26097,15 @@
       <c r="D12" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="13" t="n">
         <f aca="false">PL!F13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="11" t="n">
         <f aca="false">B12*E12</f>
         <v>4499.37831801015</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <f aca="false">F12/px-1</f>
         <v>0.740571883176075</v>
       </c>
@@ -25146,15 +26124,15 @@
       <c r="D13" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="13" t="n">
         <f aca="false">PL!G13</f>
         <v>129.466094073693</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="11" t="n">
         <f aca="false">B13*E13</f>
         <v>1941.99141110539</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="12" t="n">
         <f aca="false">F13/px-1</f>
         <v>-0.248746069204877</v>
       </c>
@@ -25173,15 +26151,15 @@
       <c r="D14" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="13" t="n">
         <f aca="false">PL!G13</f>
         <v>129.466094073693</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="11" t="n">
         <f aca="false">B14*E14</f>
         <v>2654.0549285107</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="12" t="n">
         <f aca="false">F14/px-1</f>
         <v>0.0267137054200013</v>
       </c>
@@ -25200,15 +26178,15 @@
       <c r="D15" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="13" t="n">
         <f aca="false">PL!G13</f>
         <v>129.466094073693</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="11" t="n">
         <f aca="false">B15*E15</f>
         <v>4233.54127620976</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="12" t="n">
         <f aca="false">F15/px-1</f>
         <v>0.637733569133368</v>
       </c>
@@ -25227,15 +26205,15 @@
       <c r="D16" s="0" t="s">
         <v>456</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="13" t="n">
         <f aca="false">PL!I13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="11" t="n">
         <f aca="false">B16*E16</f>
         <v>2063.93500826154</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="12" t="n">
         <f aca="false">F16/px-1</f>
         <v>-0.201572530653177</v>
       </c>
@@ -25254,15 +26232,15 @@
       <c r="D17" s="0" t="s">
         <v>456</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <f aca="false">PL!I13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="11" t="n">
         <f aca="false">B17*E17</f>
         <v>2820.71117795744</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="12" t="n">
         <f aca="false">F17/px-1</f>
         <v>0.0911842081073253</v>
       </c>
@@ -25281,15 +26259,15 @@
       <c r="D18" s="0" t="s">
         <v>456</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <f aca="false">PL!I13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="11" t="n">
         <f aca="false">B18*E18</f>
         <v>4499.37831801015</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="12" t="n">
         <f aca="false">F18/px-1</f>
         <v>0.740571883176075</v>
       </c>
@@ -25308,15 +26286,15 @@
       <c r="D19" s="0" t="s">
         <v>456</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="13" t="n">
         <f aca="false">PL!J13</f>
         <v>106.34571226785</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="11" t="n">
         <f aca="false">B19*E19</f>
         <v>1595.18568401774</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="12" t="n">
         <f aca="false">F19/px-1</f>
         <v>-0.382906892062769</v>
       </c>
@@ -25335,15 +26313,15 @@
       <c r="D20" s="0" t="s">
         <v>456</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="13" t="n">
         <f aca="false">PL!J13</f>
         <v>106.34571226785</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="11" t="n">
         <f aca="false">B20*E20</f>
         <v>2180.08710149092</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="12" t="n">
         <f aca="false">F20/px-1</f>
         <v>-0.15663941915245</v>
       </c>
@@ -25362,15 +26340,15 @@
       <c r="D21" s="0" t="s">
         <v>456</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="13" t="n">
         <f aca="false">PL!J13</f>
         <v>106.34571226785</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="11" t="n">
         <f aca="false">B21*E21</f>
         <v>3477.50479115868</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="12" t="n">
         <f aca="false">F21/px-1</f>
         <v>0.345262975303165</v>
       </c>
@@ -25429,15 +26407,15 @@
       <c r="A4" s="0" t="s">
         <v>463</v>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="16" t="n">
         <f aca="false">PL!B5</f>
         <v>34.326</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="16" t="n">
         <f aca="false">rev25*ai25_share*(1+ai_cagr)</f>
         <v>34.598718</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <f aca="false">B4/C4-1</f>
         <v>-0.00788231517711135</v>
       </c>
@@ -25449,15 +26427,15 @@
       <c r="A5" s="0" t="s">
         <v>465</v>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="16" t="n">
         <f aca="false">PL!B4</f>
         <v>28.605</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="16" t="n">
         <f aca="false">rev25*ai25_share*(1+ai_cagr)</f>
         <v>34.598718</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <f aca="false">B5/C5-1</f>
         <v>-0.173235262647593</v>
       </c>
@@ -25469,15 +26447,15 @@
       <c r="A6" s="0" t="s">
         <v>467</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="16" t="n">
         <f aca="false">PL!B13</f>
         <v>112.095299667786</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <f aca="false">cons_eps26</f>
         <v>107.6</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <f aca="false">B6/C6-1</f>
         <v>0.0417778779533982</v>
       </c>
@@ -25489,15 +26467,15 @@
       <c r="A7" s="0" t="s">
         <v>468</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="16" t="n">
         <f aca="false">PL!B7</f>
         <v>176.12</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <f aca="false">rev25*(1+g26_guid)</f>
         <v>176.2992</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <f aca="false">B7/C7-1</f>
         <v>-0.00101645384664262</v>
       </c>
@@ -25509,15 +26487,15 @@
       <c r="A8" s="0" t="s">
         <v>470</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <f aca="false">PL!B13</f>
         <v>112.095299667786</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <f aca="false">eps26_1to3q+ntd26_4q*opm26_4q*ni_op_26/shares</f>
         <v>112.100961063852</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <f aca="false">B8/C8-1</f>
         <v>-5.0502654148521E-005</v>
       </c>
@@ -25529,15 +26507,15 @@
       <c r="A9" s="0" t="s">
         <v>472</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <f aca="false">PL!C7</f>
         <v>225.63296</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <f aca="false">cons_rev27</f>
         <v>229</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <f aca="false">B9/C9-1</f>
         <v>-0.0147032314410479</v>
       </c>
@@ -25549,15 +26527,15 @@
       <c r="A10" s="0" t="s">
         <v>473</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="16" t="n">
         <f aca="false">PL!C13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <f aca="false">cons_eps27</f>
         <v>142</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <f aca="false">B10/C10-1</f>
         <v>-0.0310164280462261</v>
       </c>
@@ -25569,15 +26547,15 @@
       <c r="A11" s="0" t="s">
         <v>474</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <f aca="false">CoWoS!B13</f>
         <v>1107.85762580894</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <f aca="false">ms_dem26</f>
         <v>1394</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <f aca="false">B11/C11-1</f>
         <v>-0.205267126392436</v>
       </c>
@@ -25589,15 +26567,15 @@
       <c r="A12" s="0" t="s">
         <v>475</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="16" t="n">
         <f aca="false">CoWoS!C13</f>
         <v>2096.42857142857</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <f aca="false">ms_dem27</f>
         <v>2509</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <f aca="false">B12/C12-1</f>
         <v>-0.16443659966976</v>
       </c>
@@ -25637,13 +26615,13 @@
       <c r="A3" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>478</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>480</v>
       </c>
     </row>
@@ -25651,15 +26629,15 @@
       <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="13" t="n">
         <f aca="false">(PL!C7)*(gm27_A-opex)*ni_op*fx/shares</f>
         <v>137.595667217436</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="12" t="n">
         <f aca="false">B4/B$4-1</f>
         <v>0</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <f aca="false">CoWoS!C17</f>
         <v>0.962547553456644</v>
       </c>
@@ -25668,15 +26646,15 @@
       <c r="A5" s="0" t="s">
         <v>481</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="13" t="n">
         <f aca="false">(PL!C7-0.3*u_rb_27*ct_VR*(1+px27)*(1+ai_oth))*(gm27_A-opex)*ni_op*fx/shares</f>
         <v>132.776424358447</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <f aca="false">B5/B$4-1</f>
         <v>-0.0350246701545733</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <f aca="false">(CoWoS!C13-0.3*CoWoS!C5)/CoWoS!C16</f>
         <v>0.842024137478683</v>
       </c>
@@ -25685,15 +26663,15 @@
       <c r="A6" s="0" t="s">
         <v>482</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <f aca="false">(PL!C7-PL!C5*px27/(1+px27))*(gm27_A-opex)*ni_op*fx/shares</f>
         <v>133.229545589358</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <f aca="false">B6/B$4-1</f>
         <v>-0.0317315342581156</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <f aca="false">CoWoS!C17</f>
         <v>0.962547553456644</v>
       </c>
@@ -25702,15 +26680,15 @@
       <c r="A7" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <f aca="false">(PL!C7)*(0.6-opex)*ni_op*fx/shares</f>
         <v>127.85438104275</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <f aca="false">B7/B$4-1</f>
         <v>-0.0707964601769913</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <f aca="false">CoWoS!C17</f>
         <v>0.962547553456644</v>
       </c>
@@ -25719,15 +26697,15 @@
       <c r="A8" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <f aca="false">(PL!C7)*(0.67-opex)*ni_op*fx/shares</f>
         <v>144.90163184845</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <f aca="false">B8/B$4-1</f>
         <v>0.0530973451327432</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <f aca="false">CoWoS!C17</f>
         <v>0.962547553456644</v>
       </c>
@@ -25736,15 +26714,15 @@
       <c r="A9" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <f aca="false">(PL!C7-PL!B6*na27_A)*(gm27_A-opex)*ni_op*fx/shares</f>
         <v>127.21939592936</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <f aca="false">B9/B$4-1</f>
         <v>-0.0754113228847417</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <f aca="false">CoWoS!C17</f>
         <v>0.962547553456644</v>
       </c>
@@ -25753,15 +26731,15 @@
       <c r="A10" s="0" t="s">
         <v>486</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <f aca="false">(PL!C7)*(gm27_A-opex)*ni_op*fx/shares</f>
         <v>137.595667217436</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <f aca="false">B10/B$4-1</f>
         <v>0</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <f aca="false">CoWoS!C13/((cap_end26+170)/2*12*(1+osat))</f>
         <v>1.05880230880231</v>
       </c>
@@ -25778,13 +26756,13 @@
       <c r="B14" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>478</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>490</v>
       </c>
       <c r="F14" s="4" t="s">
@@ -25795,23 +26773,23 @@
       <c r="A15" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="9" t="n">
         <f aca="false">ni_op</f>
         <v>0.874593626904623</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="13" t="n">
         <f aca="false">PL!C11*B15*fx/shares</f>
         <v>137.595667217436</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <f aca="false">C15/C$15-1</f>
         <v>0</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="13" t="n">
         <f aca="false">PL!D11*B15*fx/shares</f>
         <v>157.640285107059</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="14" t="n">
         <f aca="false">E15/E$15-1</f>
         <v>0</v>
       </c>
@@ -25820,50 +26798,50 @@
       <c r="A16" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="9" t="n">
         <f aca="false">ni_op_lo</f>
-        <v>0.887</v>
-      </c>
-      <c r="C16" s="12" t="n">
+        <v>0.864414533026079</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <f aca="false">PL!C11*B16*fx/shares</f>
-        <v>139.547503054439</v>
-      </c>
-      <c r="D16" s="13" t="n">
+        <v>135.994238655872</v>
+      </c>
+      <c r="D16" s="14" t="n">
         <f aca="false">C16/C$15-1</f>
-        <v>0.0141853001368031</v>
-      </c>
-      <c r="E16" s="12" t="n">
+        <v>-0.0116386554456953</v>
+      </c>
+      <c r="E16" s="13" t="n">
         <f aca="false">PL!D11*B16*fx/shares</f>
-        <v>159.876459864953</v>
-      </c>
-      <c r="F16" s="13" t="n">
+        <v>155.805564144336</v>
+      </c>
+      <c r="F16" s="14" t="n">
         <f aca="false">E16/E$15-1</f>
-        <v>0.0141853001368029</v>
+        <v>-0.0116386554456953</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="9" t="n">
         <f aca="false">ni_op_hi</f>
-        <v>0.92</v>
-      </c>
-      <c r="C17" s="12" t="n">
+        <v>0.909166874667651</v>
+      </c>
+      <c r="C17" s="13" t="n">
         <f aca="false">PL!C11*B17*fx/shares</f>
-        <v>144.73923653899</v>
-      </c>
-      <c r="D17" s="13" t="n">
+        <v>143.034912310799</v>
+      </c>
+      <c r="D17" s="14" t="n">
         <f aca="false">C17/C$15-1</f>
-        <v>0.0519171094992772</v>
-      </c>
-      <c r="E17" s="12" t="n">
+        <v>0.0395306422313984</v>
+      </c>
+      <c r="E17" s="13" t="n">
         <f aca="false">PL!D11*B17*fx/shares</f>
-        <v>165.824513050459</v>
-      </c>
-      <c r="F17" s="13" t="n">
+        <v>163.871906818881</v>
+      </c>
+      <c r="F17" s="14" t="n">
         <f aca="false">E17/E$15-1</f>
-        <v>0.051917109499277</v>
+        <v>0.0395306422313984</v>
       </c>
     </row>
   </sheetData>
@@ -25882,7 +26860,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60"/>
@@ -25956,35 +26934,35 @@
       <c r="C4" s="17" t="n">
         <v>22.91</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="16" t="n">
         <f aca="false">B4+C4</f>
         <v>1144.19</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="16" t="n">
         <f aca="false">D4-F4</f>
         <v>127.29</v>
       </c>
       <c r="F4" s="17" t="n">
         <v>1016.9</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
       <c r="I4" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="13" t="n">
+      <c r="J4" s="14" t="n">
         <f aca="false">E4/D4</f>
         <v>0.111249005846931</v>
       </c>
-      <c r="K4" s="13" t="n">
+      <c r="K4" s="14" t="n">
         <f aca="false">C4/B4</f>
         <v>0.0204320062785388</v>
       </c>
-      <c r="L4" s="16" t="n">
+      <c r="L4" s="9" t="n">
         <f aca="false">F4/(D4-E4)</f>
         <v>1</v>
       </c>
-      <c r="M4" s="16" t="n">
+      <c r="M4" s="9" t="n">
         <f aca="false">F4/B4</f>
         <v>0.906909960045662</v>
       </c>
@@ -26008,7 +26986,7 @@
       <c r="C5" s="17" t="n">
         <v>57.71</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <f aca="false">B5+C5</f>
         <v>979.18</v>
       </c>
@@ -26021,23 +26999,23 @@
       <c r="G5" s="17" t="n">
         <v>60.29</v>
       </c>
-      <c r="H5" s="15"/>
+      <c r="H5" s="16"/>
       <c r="I5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <f aca="false">E5/D5</f>
         <v>0.144406544251312</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="K5" s="14" t="n">
         <f aca="false">C5/B5</f>
         <v>0.0626281919107513</v>
       </c>
-      <c r="L5" s="16" t="n">
+      <c r="L5" s="9" t="n">
         <f aca="false">F5/(D5-E5)</f>
         <v>0.999988063692139</v>
       </c>
-      <c r="M5" s="16" t="n">
+      <c r="M5" s="9" t="n">
         <f aca="false">F5/B5</f>
         <v>0.909166874667651</v>
       </c>
@@ -26061,7 +27039,7 @@
       <c r="C6" s="17" t="n">
         <v>83.79</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="16" t="n">
         <f aca="false">B6+C6</f>
         <v>1405.84</v>
       </c>
@@ -26080,19 +27058,19 @@
       <c r="I6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="14" t="n">
         <f aca="false">E6/D6</f>
         <v>0.166028851078359</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="K6" s="14" t="n">
         <f aca="false">C6/B6</f>
         <v>0.063378843462804</v>
       </c>
-      <c r="L6" s="16" t="n">
+      <c r="L6" s="9" t="n">
         <f aca="false">F6/(D6-E6)</f>
         <v>1</v>
       </c>
-      <c r="M6" s="16" t="n">
+      <c r="M6" s="9" t="n">
         <f aca="false">F6/B6</f>
         <v>0.886827275821641</v>
       </c>
@@ -26116,7 +27094,7 @@
       <c r="C7" s="17" t="n">
         <v>105.56</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <f aca="false">B7+C7</f>
         <v>2041.65</v>
       </c>
@@ -26135,19 +27113,19 @@
       <c r="I7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <f aca="false">E7/D7</f>
         <v>0.159797222834472</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="14" t="n">
         <f aca="false">C7/B7</f>
         <v>0.0545222587792923</v>
       </c>
-      <c r="L7" s="16" t="n">
+      <c r="L7" s="9" t="n">
         <f aca="false">F7/(D7-E7)</f>
         <v>1</v>
       </c>
-      <c r="M7" s="16" t="n">
+      <c r="M7" s="9" t="n">
         <f aca="false">F7/B7</f>
         <v>0.886012530409227</v>
       </c>
@@ -26165,42 +27143,42 @@
       <c r="A8" s="0" t="s">
         <v>516</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <f aca="false">ntd26_1q*opm26_1q</f>
         <v>658.9121</v>
       </c>
       <c r="C8" s="17" t="n">
         <v>28.83</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <f aca="false">B8+C8</f>
         <v>687.7421</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="16" t="n">
         <f aca="false">D8-F8</f>
         <v>115.2621</v>
       </c>
       <c r="F8" s="17" t="n">
         <v>572.48</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
       <c r="I8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="14" t="n">
         <f aca="false">E8/D8</f>
         <v>0.167594945837982</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="14" t="n">
         <f aca="false">C8/B8</f>
         <v>0.0437539392583624</v>
       </c>
-      <c r="L8" s="16" t="n">
+      <c r="L8" s="9" t="n">
         <f aca="false">F8/(D8-E8)</f>
         <v>1</v>
       </c>
-      <c r="M8" s="16" t="n">
+      <c r="M8" s="9" t="n">
         <f aca="false">F8/B8</f>
         <v>0.868826054340177</v>
       </c>
@@ -26218,14 +27196,14 @@
       <c r="A9" s="0" t="s">
         <v>518</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <f aca="false">ntd26_2q*opm26_2q</f>
         <v>766.03914</v>
       </c>
       <c r="C9" s="17" t="n">
         <v>95.83</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <f aca="false">B9+C9</f>
         <v>861.86914</v>
       </c>
@@ -26235,24 +27213,24 @@
       <c r="F9" s="17" t="n">
         <v>706.56</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
       <c r="I9" s="17" t="n">
         <v>63.2</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="14" t="n">
         <f aca="false">E9/D9</f>
         <v>0.180595861687309</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="14" t="n">
         <f aca="false">C9/B9</f>
         <v>0.125098046556733</v>
       </c>
-      <c r="L9" s="16" t="n">
+      <c r="L9" s="9" t="n">
         <f aca="false">F9/(D9-E9)</f>
         <v>1.00048265471819</v>
       </c>
-      <c r="M9" s="16" t="n">
+      <c r="M9" s="9" t="n">
         <f aca="false">F9/B9</f>
         <v>0.922354959565121</v>
       </c>
@@ -26276,7 +27254,7 @@
       <c r="C10" s="17" t="n">
         <v>34.59</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <f aca="false">B10+C10</f>
         <v>911.04</v>
       </c>
@@ -26286,32 +27264,32 @@
       <c r="F10" s="17" t="n">
         <v>763.06</v>
       </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
       <c r="I10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="14" t="n">
         <f aca="false">E10/D10</f>
         <v>0.162122409553916</v>
       </c>
-      <c r="K10" s="13" t="n">
+      <c r="K10" s="14" t="n">
         <f aca="false">C10/B10</f>
         <v>0.0394660277254835</v>
       </c>
-      <c r="L10" s="16" t="n">
+      <c r="L10" s="9" t="n">
         <f aca="false">F10/(D10-E10)</f>
         <v>0.999633190976498</v>
       </c>
-      <c r="M10" s="16" t="n">
+      <c r="M10" s="9" t="n">
         <f aca="false">F10/B10</f>
         <v>0.870625820069599</v>
       </c>
       <c r="N10" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>508</v>
+        <v>212</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>522</v>
@@ -26321,45 +27299,45 @@
       <c r="A11" s="0" t="s">
         <v>523</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <f aca="false">SUM(B8:B10)</f>
         <v>2301.40124</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <f aca="false">SUM(C8:C10)</f>
         <v>159.25</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <f aca="false">SUM(D8:D10)</f>
         <v>2460.65124</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="16" t="n">
         <f aca="false">SUM(E8:E10)</f>
         <v>418.6121</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="16" t="n">
         <f aca="false">SUM(F8:F10)</f>
         <v>2042.1</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15" t="n">
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16" t="n">
         <f aca="false">SUM(I8:I10)</f>
         <v>63.2</v>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="J11" s="14" t="n">
         <f aca="false">E11/D11</f>
         <v>0.170122483509691</v>
       </c>
-      <c r="K11" s="13" t="n">
+      <c r="K11" s="14" t="n">
         <f aca="false">C11/B11</f>
         <v>0.0691969732318385</v>
       </c>
-      <c r="L11" s="16" t="n">
+      <c r="L11" s="9" t="n">
         <f aca="false">F11/(D11-E11)</f>
         <v>1.00002980354236</v>
       </c>
-      <c r="M11" s="16" t="n">
+      <c r="M11" s="9" t="n">
         <f aca="false">F11/B11</f>
         <v>0.887328973543092</v>
       </c>
@@ -26379,7 +27357,7 @@
       <c r="A14" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
         <f aca="false">(E6+E7+E11)/(D6+D7+D11)</f>
         <v>0.165580350953154</v>
       </c>
@@ -26391,7 +27369,7 @@
       <c r="A15" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <f aca="false">(SUM(C4:C7)+C11-I11)/(SUM(B4:B7)+B11)</f>
         <v>0.0481460113069807</v>
       </c>
@@ -26403,7 +27381,7 @@
       <c r="A16" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="9" t="n">
         <f aca="false">(1+B15)*(1-B14)</f>
         <v>0.874593626904623</v>
       </c>
@@ -26415,7 +27393,7 @@
       <c r="A17" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="9" t="n">
         <f aca="false">(F6+F7)/(B6+B7)</f>
         <v>0.886343128287919</v>
       </c>
@@ -26424,7 +27402,7 @@
       <c r="A18" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="9" t="n">
         <f aca="false">M11</f>
         <v>0.887328973543092</v>
       </c>
@@ -26436,17 +27414,58 @@
       <c r="A19" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="9" t="n">
         <f aca="false">(F11-I11*(1-B14))/B11</f>
         <v>0.864414533026079</v>
       </c>
-      <c r="P19" s="6" t="s">
+      <c r="P19" s="8" t="s">
         <v>536</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <f aca="false">M5</f>
+        <v>0.909166874667651</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>537</v>
+        <v>539</v>
+      </c>
+      <c r="B21" s="14" t="n">
+        <f aca="false">(SUM(C4:C7)+C11)/(SUM(B4:B7)+B11)</f>
+        <v>0.0564592945007984</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="B22" s="9" t="n">
+        <f aca="false">(1+B21)*(1-B14)</f>
+        <v>0.881530393749635</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -26465,7 +27484,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -26474,276 +27493,316 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>603</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>604</v>
+        <v>610</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>605</v>
+      <c r="A35" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>621</v>
       </c>
     </row>
   </sheetData>

--- a/tsmc/dist/20261022_台積電模型_v0.2.xlsx
+++ b/tsmc/dist/20261022_台積電模型_v0.2.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
@@ -234,7 +234,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="661">
   <si>
     <r>
       <rPr>
@@ -15147,777 +15147,13 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Recon — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本模型 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司口徑、共識（只作事後對照）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">本模型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">對照值</t>
-  </si>
-  <si>
-    <t xml:space="preserve">差距</t>
-  </si>
-  <si>
-    <t xml:space="preserve">對照來源</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相關營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司口徑推算</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025 AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加速器十幾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">後段 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× CAGR 57%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（公司）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加速器內容（不含其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同上</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相關（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ai_oth</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Assumed</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 EPS vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共識</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司全年成長指引（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025 × (1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44%)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">法說：全年美元成長約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 EPS vs 1–3Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">實績＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">指引推算</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司各季 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 22.08</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">27.25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">29.43</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">指引中點</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共識</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共識</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 CoWoS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">需求 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs Morgan Stanley</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 CoWoS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">需求 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs Morgan Stanley</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sens — 2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：一次動一個輸入</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">輸入</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027 EPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相對基準</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <rFont val="Cambria"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2027 CoWoS </t>
+      <t xml:space="preserve">6. </t>
     </r>
     <r>
       <rPr>
@@ -15926,7 +15162,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">需求 </t>
+      <t xml:space="preserve">十年倍數與規則值（</t>
     </r>
     <r>
       <rPr>
@@ -15936,7 +15172,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">÷ </t>
+      <t xml:space="preserve">2016–2025 </t>
     </r>
     <r>
       <rPr>
@@ -15945,230 +15181,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">產能</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rubin </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆數 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">內容價格 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 +0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（不漲）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">毛利率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 60%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">毛利率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 67%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 +0%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoWoS 2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年底產能 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">萬片（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">KGI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">淨利 </t>
+      <t xml:space="preserve">年底；見頂年 </t>
     </r>
     <r>
       <rPr>
@@ -16178,7 +15191,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">÷ </t>
+      <t xml:space="preserve">25 </t>
     </r>
     <r>
       <rPr>
@@ -16187,7 +15200,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">營業利益 對 </t>
+      <t xml:space="preserve">分位、中段中位數、谷底 </t>
     </r>
     <r>
       <rPr>
@@ -16197,7 +15210,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">EPS </t>
+      <t xml:space="preserve">75 </t>
     </r>
     <r>
       <rPr>
@@ -16206,8 +15219,135 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">的影響（情境 </t>
-    </r>
+      <t xml:space="preserve">分位）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：合理倍數＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2016–2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">依循環位置取分位；台積電 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為中段，取中位數，區間為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位。兩個來源各自取分位再平均、四捨五入到兩位。倍數歷史為輸入（藍字）。</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -16216,7 +15356,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">P/E</t>
     </r>
     <r>
       <rPr>
@@ -16225,277 +15365,170 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">設定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">比值</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2028 EPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">基準（推導值）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">淨利 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.864</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（低）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">淨利 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.909</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（高）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NI_OI — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">淨利 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益拆解（新台幣十億）。淨利</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益 ＝ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋營業外</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) × (1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">－有效稅率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) × </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">少數股權等調整。藍字＝輸入</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">期間</t>
-  </si>
-  <si>
-    <t xml:space="preserve">營業外收支</t>
-  </si>
-  <si>
-    <t xml:space="preserve">稅前淨利</t>
-  </si>
-  <si>
-    <t xml:space="preserve">所得稅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">利息收入</t>
-  </si>
-  <si>
-    <t xml:space="preserve">匯兌損益</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一次性項目</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有效稅率</t>
+      <t xml:space="preserve">：十年歷史倍數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">年底</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FullRatio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">companiesmarketcap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">標記／說明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FullRatio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Interested-party</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">companiesmarketcap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（各來源）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">中位數（各來源）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（各來源）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最小（各來源）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最大（各來源）</t>
   </si>
   <si>
     <r>
@@ -16505,7 +15538,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">營業外</t>
+      <t xml:space="preserve">採用 </t>
     </r>
     <r>
       <rPr>
@@ -16515,7 +15548,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">÷</t>
+      <t xml:space="preserve">25 </t>
     </r>
     <r>
       <rPr>
@@ -16524,21 +15557,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">營業利益</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">少數股權等調整</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">淨利</t>
+      <t xml:space="preserve">分位（</t>
     </r>
     <r>
       <rPr>
@@ -16548,25 +15567,1950 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最小（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用 最大（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：規則值</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">循環位置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股基準</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現價 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基準</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：中段（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">中段 → 中位數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：低（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（區間下緣）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：高（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位（區間上緣）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">規則值：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參考：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C × 75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Recon — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本模型 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司口徑、共識（只作事後對照）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">本模型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">對照值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">差距</t>
+  </si>
+  <si>
+    <t xml:space="preserve">對照來源</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相關營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司口徑推算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加速器十幾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後段 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× CAGR 57%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（公司）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加速器內容（不含其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同上</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相關（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ai_oth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 EPS vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共識</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司全年成長指引（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 × (1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法說：全年美元成長約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 EPS vs 1–3Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">實績＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">指引推算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS 22.08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27.25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29.43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">指引中點</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共識</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共識</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 CoWoS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">需求 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs Morgan Stanley</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 CoWoS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">需求 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs Morgan Stanley</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sens — 2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：一次動一個輸入</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">輸入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027 EPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">相對基準</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 CoWoS </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">需求 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">產能</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">內容價格 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 +0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不漲）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 60%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 67%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 +0%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CoWoS 2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底產能 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">萬片（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KGI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">淨利 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益 對 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的影響（情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">設定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">比值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028 EPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基準（推導值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">淨利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.864</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（低）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">淨利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.909</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（高）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NI_OI — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">淨利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益拆解（新台幣十億）。淨利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">÷</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益 ＝ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋營業外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) × (1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">－有效稅率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">少數股權等調整。藍字＝輸入</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">期間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">營業外收支</t>
+  </si>
+  <si>
+    <t xml:space="preserve">稅前淨利</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所得稅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">利息收入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">匯兌損益</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一次性項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有效稅率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">營業外</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">營業利益</t>
     </r>
   </si>
   <si>
+    <t xml:space="preserve">少數股權等調整</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">淨利</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">獨立來源數</t>
   </si>
   <si>
-    <t xml:space="preserve">2022</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -16656,9 +17600,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">2023</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -16765,9 +17706,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">2024</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -16872,9 +17810,6 @@
       </rPr>
       <t xml:space="preserve">／財報一個來源</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2025</t>
   </si>
   <si>
     <r>
@@ -21297,7 +22232,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
@@ -21305,7 +22240,8 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="0.0\x"/>
-    <numFmt numFmtId="171" formatCode="#,##0.0"/>
+    <numFmt numFmtId="171" formatCode="0.00"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -21416,7 +22352,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -21481,11 +22417,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -25828,10 +26772,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
@@ -26356,6 +27301,413 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
         <v>457</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="B31" s="16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B32" s="16" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B33" s="16" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="B36" s="16" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="B37" s="16" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B38" s="16" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="B39" s="16" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B40" s="16" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="B41" s="17" t="n">
+        <f aca="false">PERCENTILE(B31:B40,0.25)</f>
+        <v>16.525</v>
+      </c>
+      <c r="C41" s="17" t="n">
+        <f aca="false">PERCENTILE(C31:C40,0.25)</f>
+        <v>14.35</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="B42" s="17" t="n">
+        <f aca="false">MEDIAN(B31:B40)</f>
+        <v>22.54</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <f aca="false">MEDIAN(C31:C40)</f>
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B43" s="17" t="n">
+        <f aca="false">PERCENTILE(B31:B40,0.75)</f>
+        <v>28.9525</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <f aca="false">PERCENTILE(C31:C40,0.75)</f>
+        <v>28.025</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="B44" s="17" t="n">
+        <f aca="false">MIN(B31:B40)</f>
+        <v>11.94</v>
+      </c>
+      <c r="C44" s="17" t="n">
+        <f aca="false">MIN(C31:C40)</f>
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="B45" s="17" t="n">
+        <f aca="false">MAX(B31:B40)</f>
+        <v>31.11</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <f aca="false">MAX(C31:C40)</f>
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B46" s="17" t="n">
+        <f aca="false">ROUND(AVERAGE(B41,C41),2)</f>
+        <v>15.44</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B47" s="17" t="n">
+        <f aca="false">ROUND(AVERAGE(B42,C42),2)</f>
+        <v>21.97</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B48" s="17" t="n">
+        <f aca="false">ROUND(AVERAGE(B43,C43),2)</f>
+        <v>28.49</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B49" s="17" t="n">
+        <f aca="false">ROUND(MIN(B44,C44),2)</f>
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B50" s="17" t="n">
+        <f aca="false">ROUND(MAX(B45,C45),2)</f>
+        <v>31.11</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="C54" s="17" t="n">
+        <f aca="false">B47</f>
+        <v>21.97</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="E54" s="13" t="n">
+        <f aca="false">PL!C13</f>
+        <v>137.595667217436</v>
+      </c>
+      <c r="F54" s="18" t="n">
+        <f aca="false">C54*E54</f>
+        <v>3022.97680876707</v>
+      </c>
+      <c r="G54" s="14" t="n">
+        <f aca="false">F54/px-1</f>
+        <v>0.169430100103314</v>
+      </c>
+      <c r="H54" s="17" t="n">
+        <f aca="false">px/E54</f>
+        <v>18.7869287767256</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <f aca="false">B46</f>
+        <v>15.44</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <f aca="false">PL!C13</f>
+        <v>137.595667217436</v>
+      </c>
+      <c r="F55" s="18" t="n">
+        <f aca="false">C55*E55</f>
+        <v>2124.47710183721</v>
+      </c>
+      <c r="G55" s="14" t="n">
+        <f aca="false">F55/px-1</f>
+        <v>-0.178151991552336</v>
+      </c>
+      <c r="H55" s="17" t="n">
+        <f aca="false">px/E55</f>
+        <v>18.7869287767256</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>497</v>
+      </c>
+      <c r="C56" s="17" t="n">
+        <f aca="false">B48</f>
+        <v>28.49</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <f aca="false">PL!C13</f>
+        <v>137.595667217436</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <f aca="false">C56*E56</f>
+        <v>3920.10055902475</v>
+      </c>
+      <c r="G56" s="14" t="n">
+        <f aca="false">F56/px-1</f>
+        <v>0.5164799067794</v>
+      </c>
+      <c r="H56" s="17" t="n">
+        <f aca="false">px/E56</f>
+        <v>18.7869287767256</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="C57" s="17" t="n">
+        <f aca="false">B48</f>
+        <v>28.49</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="E57" s="13" t="n">
+        <f aca="false">PL!J13</f>
+        <v>106.34571226785</v>
+      </c>
+      <c r="F57" s="18" t="n">
+        <f aca="false">C57*E57</f>
+        <v>3029.78934251103</v>
+      </c>
+      <c r="G57" s="14" t="n">
+        <f aca="false">F57/px-1</f>
+        <v>0.172065509675448</v>
+      </c>
+      <c r="H57" s="17" t="n">
+        <f aca="false">px/E57</f>
+        <v>24.3075150363302</v>
       </c>
     </row>
   </sheetData>
@@ -26383,7 +27735,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>458</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26391,27 +27743,27 @@
         <v>14</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>459</v>
+        <v>502</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>460</v>
+        <v>503</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>461</v>
+        <v>504</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>463</v>
-      </c>
-      <c r="B4" s="16" t="n">
+        <v>506</v>
+      </c>
+      <c r="B4" s="18" t="n">
         <f aca="false">PL!B5</f>
         <v>34.326</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="18" t="n">
         <f aca="false">rev25*ai25_share*(1+ai_cagr)</f>
         <v>34.598718</v>
       </c>
@@ -26420,18 +27772,18 @@
         <v>-0.00788231517711135</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>464</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="B5" s="16" t="n">
+        <v>508</v>
+      </c>
+      <c r="B5" s="18" t="n">
         <f aca="false">PL!B4</f>
         <v>28.605</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="18" t="n">
         <f aca="false">rev25*ai25_share*(1+ai_cagr)</f>
         <v>34.598718</v>
       </c>
@@ -26440,18 +27792,18 @@
         <v>-0.173235262647593</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>466</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>467</v>
-      </c>
-      <c r="B6" s="16" t="n">
+        <v>510</v>
+      </c>
+      <c r="B6" s="18" t="n">
         <f aca="false">PL!B13</f>
         <v>112.095299667786</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="18" t="n">
         <f aca="false">cons_eps26</f>
         <v>107.6</v>
       </c>
@@ -26465,13 +27817,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>468</v>
-      </c>
-      <c r="B7" s="16" t="n">
+        <v>511</v>
+      </c>
+      <c r="B7" s="18" t="n">
         <f aca="false">PL!B7</f>
         <v>176.12</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="18" t="n">
         <f aca="false">rev25*(1+g26_guid)</f>
         <v>176.2992</v>
       </c>
@@ -26480,18 +27832,18 @@
         <v>-0.00101645384664262</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>469</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>470</v>
-      </c>
-      <c r="B8" s="16" t="n">
+        <v>513</v>
+      </c>
+      <c r="B8" s="18" t="n">
         <f aca="false">PL!B13</f>
         <v>112.095299667786</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="18" t="n">
         <f aca="false">eps26_1to3q+ntd26_4q*opm26_4q*ni_op_26/shares</f>
         <v>112.100961063852</v>
       </c>
@@ -26500,18 +27852,18 @@
         <v>-5.0502654148521E-005</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>471</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>472</v>
-      </c>
-      <c r="B9" s="16" t="n">
+        <v>515</v>
+      </c>
+      <c r="B9" s="18" t="n">
         <f aca="false">PL!C7</f>
         <v>225.63296</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="18" t="n">
         <f aca="false">cons_rev27</f>
         <v>229</v>
       </c>
@@ -26525,13 +27877,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>473</v>
-      </c>
-      <c r="B10" s="16" t="n">
+        <v>516</v>
+      </c>
+      <c r="B10" s="18" t="n">
         <f aca="false">PL!C13</f>
         <v>137.595667217436</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="18" t="n">
         <f aca="false">cons_eps27</f>
         <v>142</v>
       </c>
@@ -26545,13 +27897,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>474</v>
-      </c>
-      <c r="B11" s="16" t="n">
+        <v>517</v>
+      </c>
+      <c r="B11" s="18" t="n">
         <f aca="false">CoWoS!B13</f>
         <v>1107.85762580894</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="18" t="n">
         <f aca="false">ms_dem26</f>
         <v>1394</v>
       </c>
@@ -26565,13 +27917,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>475</v>
-      </c>
-      <c r="B12" s="16" t="n">
+        <v>518</v>
+      </c>
+      <c r="B12" s="18" t="n">
         <f aca="false">CoWoS!C13</f>
         <v>2096.42857142857</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="18" t="n">
         <f aca="false">ms_dem27</f>
         <v>2509</v>
       </c>
@@ -26608,21 +27960,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>476</v>
+        <v>519</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>477</v>
+        <v>520</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>478</v>
+        <v>521</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>479</v>
+        <v>522</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>480</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26644,7 +27996,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="B5" s="13" t="n">
         <f aca="false">(PL!C7-0.3*u_rb_27*ct_VR*(1+px27)*(1+ai_oth))*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -26661,7 +28013,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>482</v>
+        <v>525</v>
       </c>
       <c r="B6" s="13" t="n">
         <f aca="false">(PL!C7-PL!C5*px27/(1+px27))*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -26678,7 +28030,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>483</v>
+        <v>526</v>
       </c>
       <c r="B7" s="13" t="n">
         <f aca="false">(PL!C7)*(0.6-opex)*ni_op*fx/shares</f>
@@ -26695,7 +28047,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>484</v>
+        <v>527</v>
       </c>
       <c r="B8" s="13" t="n">
         <f aca="false">(PL!C7)*(0.67-opex)*ni_op*fx/shares</f>
@@ -26712,7 +28064,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>485</v>
+        <v>528</v>
       </c>
       <c r="B9" s="13" t="n">
         <f aca="false">(PL!C7-PL!B6*na27_A)*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -26729,7 +28081,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>486</v>
+        <v>529</v>
       </c>
       <c r="B10" s="13" t="n">
         <f aca="false">(PL!C7)*(gm27_A-opex)*ni_op*fx/shares</f>
@@ -26746,32 +28098,32 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>487</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>488</v>
+        <v>531</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>489</v>
+        <v>532</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>478</v>
+        <v>521</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>479</v>
+        <v>522</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>490</v>
+        <v>533</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>479</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>491</v>
+        <v>534</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">ni_op</f>
@@ -26796,7 +28148,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>492</v>
+        <v>535</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">ni_op_lo</f>
@@ -26821,7 +28173,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>493</v>
+        <v>536</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">ni_op_hi</f>
@@ -26871,51 +28223,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>494</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>495</v>
+        <v>538</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>438</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>496</v>
+        <v>539</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>497</v>
+        <v>540</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>498</v>
+        <v>541</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>439</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>499</v>
+        <v>542</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>500</v>
+        <v>543</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>501</v>
+        <v>544</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>502</v>
+        <v>545</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>503</v>
+        <v>546</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>504</v>
+        <v>547</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>505</v>
+        <v>548</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>506</v>
+        <v>549</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>19</v>
@@ -26926,28 +28278,28 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="B4" s="17" t="n">
+        <v>472</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <v>1121.28</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="19" t="n">
         <v>22.91</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="18" t="n">
         <f aca="false">B4+C4</f>
         <v>1144.19</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="18" t="n">
         <f aca="false">D4-F4</f>
         <v>127.29</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="19" t="n">
         <v>1016.9</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17" t="n">
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="14" t="n">
@@ -26970,37 +28322,37 @@
         <v>1</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>508</v>
+        <v>550</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>509</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="B5" s="17" t="n">
+        <v>473</v>
+      </c>
+      <c r="B5" s="19" t="n">
         <v>921.47</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="19" t="n">
         <v>57.71</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="18" t="n">
         <f aca="false">B5+C5</f>
         <v>979.18</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="19" t="n">
         <v>141.4</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="19" t="n">
         <v>837.77</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="19" t="n">
         <v>60.29</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="17" t="n">
+      <c r="H5" s="18"/>
+      <c r="I5" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="14" t="n">
@@ -27026,36 +28378,36 @@
         <v>212</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>512</v>
-      </c>
-      <c r="B6" s="17" t="n">
+        <v>474</v>
+      </c>
+      <c r="B6" s="19" t="n">
         <v>1322.05</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="19" t="n">
         <v>83.79</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="18" t="n">
         <f aca="false">B6+C6</f>
         <v>1405.84</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="19" t="n">
         <v>233.41</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="19" t="n">
         <v>1172.43</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="19" t="n">
         <v>87.21</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="14" t="n">
@@ -27081,36 +28433,36 @@
         <v>212</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>513</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>514</v>
-      </c>
-      <c r="B7" s="17" t="n">
+        <v>475</v>
+      </c>
+      <c r="B7" s="19" t="n">
         <v>1936.09</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="19" t="n">
         <v>105.56</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="18" t="n">
         <f aca="false">B7+C7</f>
         <v>2041.65</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="19" t="n">
         <v>326.25</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="19" t="n">
         <v>1715.4</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="19" t="n">
         <v>105.74</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="19" t="n">
         <v>13.83</v>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="14" t="n">
@@ -27136,34 +28488,34 @@
         <v>212</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>516</v>
-      </c>
-      <c r="B8" s="16" t="n">
+        <v>555</v>
+      </c>
+      <c r="B8" s="18" t="n">
         <f aca="false">ntd26_1q*opm26_1q</f>
         <v>658.9121</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="19" t="n">
         <v>28.83</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="18" t="n">
         <f aca="false">B8+C8</f>
         <v>687.7421</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">D8-F8</f>
         <v>115.2621</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="19" t="n">
         <v>572.48</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17" t="n">
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="14" t="n">
@@ -27189,33 +28541,33 @@
         <v>119</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>518</v>
-      </c>
-      <c r="B9" s="16" t="n">
+        <v>557</v>
+      </c>
+      <c r="B9" s="18" t="n">
         <f aca="false">ntd26_2q*opm26_2q</f>
         <v>766.03914</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="19" t="n">
         <v>95.83</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="18" t="n">
         <f aca="false">B9+C9</f>
         <v>861.86914</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="19" t="n">
         <v>155.65</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="19" t="n">
         <v>706.56</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="17" t="n">
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19" t="n">
         <v>63.2</v>
       </c>
       <c r="J9" s="14" t="n">
@@ -27238,35 +28590,35 @@
         <v>2</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>519</v>
+        <v>558</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>521</v>
-      </c>
-      <c r="B10" s="17" t="n">
+        <v>560</v>
+      </c>
+      <c r="B10" s="19" t="n">
         <v>876.45</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="19" t="n">
         <v>34.59</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="18" t="n">
         <f aca="false">B10+C10</f>
         <v>911.04</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="19" t="n">
         <v>147.7</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="19" t="n">
         <v>763.06</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="17" t="n">
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="14" t="n">
@@ -27292,36 +28644,36 @@
         <v>212</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>523</v>
-      </c>
-      <c r="B11" s="16" t="n">
+        <v>562</v>
+      </c>
+      <c r="B11" s="18" t="n">
         <f aca="false">SUM(B8:B10)</f>
         <v>2301.40124</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="18" t="n">
         <f aca="false">SUM(C8:C10)</f>
         <v>159.25</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="18" t="n">
         <f aca="false">SUM(D8:D10)</f>
         <v>2460.65124</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">SUM(E8:E10)</f>
         <v>418.6121</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="18" t="n">
         <f aca="false">SUM(F8:F10)</f>
         <v>2042.1</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16" t="n">
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18" t="n">
         <f aca="false">SUM(I8:I10)</f>
         <v>63.2</v>
       </c>
@@ -27345,53 +28697,53 @@
         <v>119</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>524</v>
+        <v>563</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>525</v>
+        <v>564</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>526</v>
+        <v>565</v>
       </c>
       <c r="B14" s="14" t="n">
         <f aca="false">(E6+E7+E11)/(D6+D7+D11)</f>
         <v>0.165580350953154</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>527</v>
+        <v>566</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>528</v>
+        <v>567</v>
       </c>
       <c r="B15" s="14" t="n">
         <f aca="false">(SUM(C4:C7)+C11-I11)/(SUM(B4:B7)+B11)</f>
         <v>0.0481460113069807</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>530</v>
+        <v>569</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">(1+B15)*(1-B14)</f>
         <v>0.874593626904623</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>531</v>
+        <v>570</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>532</v>
+        <v>571</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">(F6+F7)/(B6+B7)</f>
@@ -27400,72 +28752,72 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>533</v>
+        <v>572</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">M11</f>
         <v>0.887328973543092</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>535</v>
+        <v>574</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">(F11-I11*(1-B14))/B11</f>
         <v>0.864414533026079</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>536</v>
+        <v>575</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>537</v>
+        <v>576</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">M5</f>
         <v>0.909166874667651</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>538</v>
+        <v>577</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>539</v>
+        <v>578</v>
       </c>
       <c r="B21" s="14" t="n">
         <f aca="false">(SUM(C4:C7)+C11)/(SUM(B4:B7)+B11)</f>
         <v>0.0564592945007984</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>540</v>
+        <v>579</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>541</v>
+        <v>580</v>
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">(1+B21)*(1-B14)</f>
         <v>0.881530393749635</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>543</v>
+        <v>582</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>544</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -27493,316 +28845,316 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>546</v>
+        <v>585</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>547</v>
+        <v>586</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>548</v>
+        <v>587</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>549</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>550</v>
+        <v>589</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>551</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>552</v>
+        <v>591</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>553</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>554</v>
+        <v>593</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>555</v>
+        <v>594</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>556</v>
+        <v>595</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>557</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>558</v>
+        <v>597</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>559</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>560</v>
+        <v>599</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>561</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>563</v>
+        <v>602</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>564</v>
+        <v>603</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>565</v>
+        <v>604</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>566</v>
+        <v>605</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>567</v>
+        <v>606</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>568</v>
+        <v>607</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>569</v>
+        <v>608</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>570</v>
+        <v>609</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>571</v>
+        <v>610</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>572</v>
+        <v>611</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>573</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>574</v>
+        <v>613</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>575</v>
+        <v>614</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>576</v>
+        <v>615</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>577</v>
+        <v>616</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>578</v>
+        <v>617</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>579</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>580</v>
+        <v>619</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>581</v>
+        <v>620</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>582</v>
+        <v>621</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>583</v>
+        <v>622</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>584</v>
+        <v>623</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>585</v>
+        <v>624</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>586</v>
+        <v>625</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>587</v>
+        <v>626</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>588</v>
+        <v>627</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>589</v>
+        <v>628</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>590</v>
+        <v>629</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>591</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>592</v>
+        <v>631</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>593</v>
+        <v>632</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>594</v>
+        <v>633</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>595</v>
+        <v>634</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>596</v>
+        <v>635</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>597</v>
+        <v>636</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>598</v>
+        <v>637</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>599</v>
+        <v>638</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>600</v>
+        <v>639</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>601</v>
+        <v>640</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>603</v>
+        <v>642</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>607</v>
+        <v>646</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>608</v>
+        <v>647</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>610</v>
+        <v>649</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>575</v>
+        <v>614</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>611</v>
+        <v>650</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>612</v>
+        <v>651</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>614</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>615</v>
+        <v>654</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>616</v>
+        <v>655</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>617</v>
+        <v>656</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>618</v>
+        <v>657</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>619</v>
+        <v>658</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>620</v>
+        <v>659</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>621</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
